--- a/results/block2_results/area/Synthetic_1/dataset_Synthetic_Synthetic_1.xlsx
+++ b/results/block2_results/area/Synthetic_1/dataset_Synthetic_Synthetic_1.xlsx
@@ -531,7 +531,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4956573926921</v>
       </c>
     </row>
     <row r="3">
@@ -575,7 +575,7 @@
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>314.1592653589793</v>
+        <v>316.495663736169</v>
       </c>
     </row>
     <row r="4">
@@ -619,7 +619,7 @@
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>314.1592653589793</v>
+        <v>316.497247714403</v>
       </c>
     </row>
     <row r="5">
@@ -663,7 +663,7 @@
         <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6184335045709</v>
       </c>
     </row>
     <row r="6">
@@ -707,7 +707,7 @@
         <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6184254719337</v>
       </c>
     </row>
     <row r="7">
@@ -751,7 +751,7 @@
         <v>5</v>
       </c>
       <c r="L7" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5201153989869</v>
       </c>
     </row>
     <row r="8">
@@ -795,7 +795,7 @@
         <v>6</v>
       </c>
       <c r="L8" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930957021824</v>
       </c>
     </row>
     <row r="9">
@@ -839,7 +839,7 @@
         <v>7</v>
       </c>
       <c r="L9" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4969575256447</v>
       </c>
     </row>
     <row r="10">
@@ -883,7 +883,7 @@
         <v>8</v>
       </c>
       <c r="L10" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4969704139756</v>
       </c>
     </row>
     <row r="11">
@@ -927,7 +927,7 @@
         <v>9</v>
       </c>
       <c r="L11" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6141132411262</v>
       </c>
     </row>
     <row r="12">
@@ -971,7 +971,7 @@
         <v>10</v>
       </c>
       <c r="L12" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6141106837076</v>
       </c>
     </row>
     <row r="13">
@@ -1015,7 +1015,7 @@
         <v>11</v>
       </c>
       <c r="L13" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5200386636117</v>
       </c>
     </row>
     <row r="14">
@@ -1059,7 +1059,7 @@
         <v>12</v>
       </c>
       <c r="L14" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930385944998</v>
       </c>
     </row>
     <row r="15">
@@ -1103,7 +1103,7 @@
         <v>13</v>
       </c>
       <c r="L15" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949762732821</v>
       </c>
     </row>
     <row r="16">
@@ -1147,7 +1147,7 @@
         <v>14</v>
       </c>
       <c r="L16" t="n">
-        <v>314.1592653589793</v>
+        <v>316.494978843572</v>
       </c>
     </row>
     <row r="17">
@@ -1191,7 +1191,7 @@
         <v>15</v>
       </c>
       <c r="L17" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930075848398</v>
       </c>
     </row>
     <row r="18">
@@ -1235,7 +1235,7 @@
         <v>16</v>
       </c>
       <c r="L18" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6130640517828</v>
       </c>
     </row>
     <row r="19">
@@ -1279,7 +1279,7 @@
         <v>17</v>
       </c>
       <c r="L19" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203838027119</v>
       </c>
     </row>
     <row r="20">
@@ -1323,7 +1323,7 @@
         <v>18</v>
       </c>
       <c r="L20" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930343464838</v>
       </c>
     </row>
     <row r="21">
@@ -1367,7 +1367,7 @@
         <v>19</v>
       </c>
       <c r="L21" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935520373542</v>
       </c>
     </row>
     <row r="22">
@@ -1411,7 +1411,7 @@
         <v>20</v>
       </c>
       <c r="L22" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949725584177</v>
       </c>
     </row>
     <row r="23">
@@ -1455,7 +1455,7 @@
         <v>21</v>
       </c>
       <c r="L23" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128876776233</v>
       </c>
     </row>
     <row r="24">
@@ -1499,7 +1499,7 @@
         <v>22</v>
       </c>
       <c r="L24" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128795357786</v>
       </c>
     </row>
     <row r="25">
@@ -1543,7 +1543,7 @@
         <v>23</v>
       </c>
       <c r="L25" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5204015809694</v>
       </c>
     </row>
     <row r="26">
@@ -1587,7 +1587,7 @@
         <v>24</v>
       </c>
       <c r="L26" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930365246085</v>
       </c>
     </row>
     <row r="27">
@@ -1631,7 +1631,7 @@
         <v>25</v>
       </c>
       <c r="L27" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935514579993</v>
       </c>
     </row>
     <row r="28">
@@ -1675,7 +1675,7 @@
         <v>26</v>
       </c>
       <c r="L28" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949767855666</v>
       </c>
     </row>
     <row r="29">
@@ -1719,7 +1719,7 @@
         <v>27</v>
       </c>
       <c r="L29" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493007424782</v>
       </c>
     </row>
     <row r="30">
@@ -1763,7 +1763,7 @@
         <v>28</v>
       </c>
       <c r="L30" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5200099873713</v>
       </c>
     </row>
     <row r="31">
@@ -1807,7 +1807,7 @@
         <v>29</v>
       </c>
       <c r="L31" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5200129880708</v>
       </c>
     </row>
     <row r="32">
@@ -1851,7 +1851,7 @@
         <v>30</v>
       </c>
       <c r="L32" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930382973014</v>
       </c>
     </row>
     <row r="33">
@@ -1895,7 +1895,7 @@
         <v>31</v>
       </c>
       <c r="L33" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935585418855</v>
       </c>
     </row>
     <row r="34">
@@ -1939,7 +1939,7 @@
         <v>32</v>
       </c>
       <c r="L34" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949722830236</v>
       </c>
     </row>
     <row r="35">
@@ -1983,7 +1983,7 @@
         <v>33</v>
       </c>
       <c r="L35" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930021386068</v>
       </c>
     </row>
     <row r="36">
@@ -2027,7 +2027,7 @@
         <v>34</v>
       </c>
       <c r="L36" t="n">
-        <v>314.1592653589793</v>
+        <v>333.612849690406</v>
       </c>
     </row>
     <row r="37">
@@ -2071,7 +2071,7 @@
         <v>35</v>
       </c>
       <c r="L37" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930389602211</v>
       </c>
     </row>
     <row r="38">
@@ -2115,7 +2115,7 @@
         <v>36</v>
       </c>
       <c r="L38" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930383625305</v>
       </c>
     </row>
     <row r="39">
@@ -2159,7 +2159,7 @@
         <v>37</v>
       </c>
       <c r="L39" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935586468697</v>
       </c>
     </row>
     <row r="40">
@@ -2203,7 +2203,7 @@
         <v>38</v>
       </c>
       <c r="L40" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949697132778</v>
       </c>
     </row>
     <row r="41">
@@ -2247,7 +2247,7 @@
         <v>39</v>
       </c>
       <c r="L41" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930027321008</v>
       </c>
     </row>
     <row r="42">
@@ -2291,7 +2291,7 @@
         <v>40</v>
       </c>
       <c r="L42" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128425862997</v>
       </c>
     </row>
     <row r="43">
@@ -2335,7 +2335,7 @@
         <v>41</v>
       </c>
       <c r="L43" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203881166635</v>
       </c>
     </row>
     <row r="44">
@@ -2379,7 +2379,7 @@
         <v>42</v>
       </c>
       <c r="L44" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930372860184</v>
       </c>
     </row>
     <row r="45">
@@ -2423,7 +2423,7 @@
         <v>43</v>
       </c>
       <c r="L45" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935613312356</v>
       </c>
     </row>
     <row r="46">
@@ -2467,7 +2467,7 @@
         <v>44</v>
       </c>
       <c r="L46" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930126274455</v>
       </c>
     </row>
     <row r="47">
@@ -2511,7 +2511,7 @@
         <v>45</v>
       </c>
       <c r="L47" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128491637729</v>
       </c>
     </row>
     <row r="48">
@@ -2555,7 +2555,7 @@
         <v>46</v>
       </c>
       <c r="L48" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128480980692</v>
       </c>
     </row>
     <row r="49">
@@ -2599,7 +2599,7 @@
         <v>47</v>
       </c>
       <c r="L49" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203733450849</v>
       </c>
     </row>
     <row r="50">
@@ -2643,7 +2643,7 @@
         <v>48</v>
       </c>
       <c r="L50" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935564731936</v>
       </c>
     </row>
     <row r="51">
@@ -2687,7 +2687,7 @@
         <v>49</v>
       </c>
       <c r="L51" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935611051667</v>
       </c>
     </row>
     <row r="52">
@@ -2731,7 +2731,7 @@
         <v>50</v>
       </c>
       <c r="L52" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949722373054</v>
       </c>
     </row>
     <row r="53">
@@ -2775,7 +2775,7 @@
         <v>51</v>
       </c>
       <c r="L53" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930090131705</v>
       </c>
     </row>
     <row r="54">
@@ -2819,7 +2819,7 @@
         <v>52</v>
       </c>
       <c r="L54" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128435143209</v>
       </c>
     </row>
     <row r="55">
@@ -2863,7 +2863,7 @@
         <v>53</v>
       </c>
       <c r="L55" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199981412842</v>
       </c>
     </row>
     <row r="56">
@@ -2907,7 +2907,7 @@
         <v>54</v>
       </c>
       <c r="L56" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493041840334</v>
       </c>
     </row>
     <row r="57">
@@ -2951,7 +2951,7 @@
         <v>55</v>
       </c>
       <c r="L57" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935596884258</v>
       </c>
     </row>
     <row r="58">
@@ -2995,7 +2995,7 @@
         <v>56</v>
       </c>
       <c r="L58" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930115302025</v>
       </c>
     </row>
     <row r="59">
@@ -3039,7 +3039,7 @@
         <v>57</v>
       </c>
       <c r="L59" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930056257696</v>
       </c>
     </row>
     <row r="60">
@@ -3083,7 +3083,7 @@
         <v>58</v>
       </c>
       <c r="L60" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128418010185</v>
       </c>
     </row>
     <row r="61">
@@ -3127,7 +3127,7 @@
         <v>59</v>
       </c>
       <c r="L61" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203859866261</v>
       </c>
     </row>
     <row r="62">
@@ -3171,7 +3171,7 @@
         <v>60</v>
       </c>
       <c r="L62" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930439535654</v>
       </c>
     </row>
     <row r="63">
@@ -3215,7 +3215,7 @@
         <v>61</v>
       </c>
       <c r="L63" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949751289681</v>
       </c>
     </row>
     <row r="64">
@@ -3259,7 +3259,7 @@
         <v>62</v>
       </c>
       <c r="L64" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949668794302</v>
       </c>
     </row>
     <row r="65">
@@ -3303,7 +3303,7 @@
         <v>63</v>
       </c>
       <c r="L65" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128459868684</v>
       </c>
     </row>
     <row r="66">
@@ -3347,7 +3347,7 @@
         <v>64</v>
       </c>
       <c r="L66" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128506817055</v>
       </c>
     </row>
     <row r="67">
@@ -3391,7 +3391,7 @@
         <v>65</v>
       </c>
       <c r="L67" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493042216251</v>
       </c>
     </row>
     <row r="68">
@@ -3435,7 +3435,7 @@
         <v>66</v>
       </c>
       <c r="L68" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930423463633</v>
       </c>
     </row>
     <row r="69">
@@ -3479,7 +3479,7 @@
         <v>67</v>
       </c>
       <c r="L69" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935605827587</v>
       </c>
     </row>
     <row r="70">
@@ -3523,7 +3523,7 @@
         <v>68</v>
       </c>
       <c r="L70" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949752365325</v>
       </c>
     </row>
     <row r="71">
@@ -3567,7 +3567,7 @@
         <v>69</v>
       </c>
       <c r="L71" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128470552172</v>
       </c>
     </row>
     <row r="72">
@@ -3611,7 +3611,7 @@
         <v>70</v>
       </c>
       <c r="L72" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128427491318</v>
       </c>
     </row>
     <row r="73">
@@ -3655,7 +3655,7 @@
         <v>71</v>
       </c>
       <c r="L73" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199964961624</v>
       </c>
     </row>
     <row r="74">
@@ -3699,7 +3699,7 @@
         <v>72</v>
       </c>
       <c r="L74" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930414946184</v>
       </c>
     </row>
     <row r="75">
@@ -3743,7 +3743,7 @@
         <v>73</v>
       </c>
       <c r="L75" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949749845024</v>
       </c>
     </row>
     <row r="76">
@@ -3787,7 +3787,7 @@
         <v>74</v>
       </c>
       <c r="L76" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930118995226</v>
       </c>
     </row>
     <row r="77">
@@ -3831,7 +3831,7 @@
         <v>75</v>
       </c>
       <c r="L77" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930069900548</v>
       </c>
     </row>
     <row r="78">
@@ -3875,7 +3875,7 @@
         <v>76</v>
       </c>
       <c r="L78" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128424507029</v>
       </c>
     </row>
     <row r="79">
@@ -3919,7 +3919,7 @@
         <v>77</v>
       </c>
       <c r="L79" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203930397376</v>
       </c>
     </row>
     <row r="80">
@@ -3963,7 +3963,7 @@
         <v>78</v>
       </c>
       <c r="L80" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935545092449</v>
       </c>
     </row>
     <row r="81">
@@ -4007,7 +4007,7 @@
         <v>79</v>
       </c>
       <c r="L81" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935641991925</v>
       </c>
     </row>
     <row r="82">
@@ -4051,7 +4051,7 @@
         <v>80</v>
       </c>
       <c r="L82" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949669798136</v>
       </c>
     </row>
     <row r="83">
@@ -4095,7 +4095,7 @@
         <v>81</v>
       </c>
       <c r="L83" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930084499521</v>
       </c>
     </row>
     <row r="84">
@@ -4139,7 +4139,7 @@
         <v>82</v>
       </c>
       <c r="L84" t="n">
-        <v>314.1592653589793</v>
+        <v>333.61284776374</v>
       </c>
     </row>
     <row r="85">
@@ -4183,7 +4183,7 @@
         <v>83</v>
       </c>
       <c r="L85" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199900746123</v>
       </c>
     </row>
     <row r="86">
@@ -4227,7 +4227,7 @@
         <v>84</v>
       </c>
       <c r="L86" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935616755819</v>
       </c>
     </row>
     <row r="87">
@@ -4271,7 +4271,7 @@
         <v>85</v>
       </c>
       <c r="L87" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935601791496</v>
       </c>
     </row>
     <row r="88">
@@ -4315,7 +4315,7 @@
         <v>86</v>
       </c>
       <c r="L88" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949672377866</v>
       </c>
     </row>
     <row r="89">
@@ -4359,7 +4359,7 @@
         <v>87</v>
       </c>
       <c r="L89" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930058181441</v>
       </c>
     </row>
     <row r="90">
@@ -4403,7 +4403,7 @@
         <v>88</v>
       </c>
       <c r="L90" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128472937596</v>
       </c>
     </row>
     <row r="91">
@@ -4447,7 +4447,7 @@
         <v>89</v>
       </c>
       <c r="L91" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203902427795</v>
       </c>
     </row>
     <row r="92">
@@ -4491,7 +4491,7 @@
         <v>90</v>
       </c>
       <c r="L92" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930425653542</v>
       </c>
     </row>
     <row r="93">
@@ -4535,7 +4535,7 @@
         <v>91</v>
       </c>
       <c r="L93" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935662898612</v>
       </c>
     </row>
     <row r="94">
@@ -4579,7 +4579,7 @@
         <v>92</v>
       </c>
       <c r="L94" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949672078131</v>
       </c>
     </row>
     <row r="95">
@@ -4623,7 +4623,7 @@
         <v>93</v>
       </c>
       <c r="L95" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493005652055</v>
       </c>
     </row>
     <row r="96">
@@ -4667,7 +4667,7 @@
         <v>94</v>
       </c>
       <c r="L96" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128473265122</v>
       </c>
     </row>
     <row r="97">
@@ -4711,7 +4711,7 @@
         <v>95</v>
       </c>
       <c r="L97" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5200024306247</v>
       </c>
     </row>
     <row r="98">
@@ -4755,7 +4755,7 @@
         <v>96</v>
       </c>
       <c r="L98" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930404442985</v>
       </c>
     </row>
     <row r="99">
@@ -4799,7 +4799,7 @@
         <v>97</v>
       </c>
       <c r="L99" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949740776408</v>
       </c>
     </row>
     <row r="100">
@@ -4843,7 +4843,7 @@
         <v>98</v>
       </c>
       <c r="L100" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949730977892</v>
       </c>
     </row>
     <row r="101">
@@ -4887,7 +4887,7 @@
         <v>99</v>
       </c>
       <c r="L101" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930132796521</v>
       </c>
     </row>
     <row r="102">
@@ -4931,7 +4931,7 @@
         <v>100</v>
       </c>
       <c r="L102" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128455768384</v>
       </c>
     </row>
     <row r="103">
@@ -4975,7 +4975,7 @@
         <v>101</v>
       </c>
       <c r="L103" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199976203734</v>
       </c>
     </row>
     <row r="104">
@@ -5019,7 +5019,7 @@
         <v>102</v>
       </c>
       <c r="L104" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930377771807</v>
       </c>
     </row>
     <row r="105">
@@ -5063,7 +5063,7 @@
         <v>103</v>
       </c>
       <c r="L105" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935643281086</v>
       </c>
     </row>
     <row r="106">
@@ -5107,7 +5107,7 @@
         <v>104</v>
       </c>
       <c r="L106" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949723935873</v>
       </c>
     </row>
     <row r="107">
@@ -5151,7 +5151,7 @@
         <v>105</v>
       </c>
       <c r="L107" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930069255237</v>
       </c>
     </row>
     <row r="108">
@@ -5195,7 +5195,7 @@
         <v>106</v>
       </c>
       <c r="L108" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128499172832</v>
       </c>
     </row>
     <row r="109">
@@ -5239,7 +5239,7 @@
         <v>107</v>
       </c>
       <c r="L109" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199980062439</v>
       </c>
     </row>
     <row r="110">
@@ -5283,7 +5283,7 @@
         <v>108</v>
       </c>
       <c r="L110" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930401126849</v>
       </c>
     </row>
     <row r="111">
@@ -5327,7 +5327,7 @@
         <v>109</v>
       </c>
       <c r="L111" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493561287317</v>
       </c>
     </row>
     <row r="112">
@@ -5371,7 +5371,7 @@
         <v>110</v>
       </c>
       <c r="L112" t="n">
-        <v>314.1592653589793</v>
+        <v>316.494972739798</v>
       </c>
     </row>
     <row r="113">
@@ -5415,7 +5415,7 @@
         <v>111</v>
       </c>
       <c r="L113" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930098691743</v>
       </c>
     </row>
     <row r="114">
@@ -5459,7 +5459,7 @@
         <v>112</v>
       </c>
       <c r="L114" t="n">
-        <v>314.1592653589793</v>
+        <v>333.61284375961</v>
       </c>
     </row>
     <row r="115">
@@ -5503,7 +5503,7 @@
         <v>113</v>
       </c>
       <c r="L115" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930379955985</v>
       </c>
     </row>
     <row r="116">
@@ -5547,7 +5547,7 @@
         <v>114</v>
       </c>
       <c r="L116" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935607472273</v>
       </c>
     </row>
     <row r="117">
@@ -5591,7 +5591,7 @@
         <v>115</v>
       </c>
       <c r="L117" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935589194494</v>
       </c>
     </row>
     <row r="118">
@@ -5635,7 +5635,7 @@
         <v>116</v>
       </c>
       <c r="L118" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949715211828</v>
       </c>
     </row>
     <row r="119">
@@ -5679,7 +5679,7 @@
         <v>117</v>
       </c>
       <c r="L119" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930138951511</v>
       </c>
     </row>
     <row r="120">
@@ -5723,7 +5723,7 @@
         <v>118</v>
       </c>
       <c r="L120" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128445192944</v>
       </c>
     </row>
     <row r="121">
@@ -5767,7 +5767,7 @@
         <v>119</v>
       </c>
       <c r="L121" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203741138454</v>
       </c>
     </row>
     <row r="122">
@@ -5811,7 +5811,7 @@
         <v>120</v>
       </c>
       <c r="L122" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493038773986</v>
       </c>
     </row>
     <row r="123">
@@ -5855,7 +5855,7 @@
         <v>121</v>
       </c>
       <c r="L123" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935613305731</v>
       </c>
     </row>
     <row r="124">
@@ -5899,7 +5899,7 @@
         <v>122</v>
       </c>
       <c r="L124" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930107030344</v>
       </c>
     </row>
     <row r="125">
@@ -5943,7 +5943,7 @@
         <v>123</v>
       </c>
       <c r="L125" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128470553886</v>
       </c>
     </row>
     <row r="126">
@@ -5987,7 +5987,7 @@
         <v>124</v>
       </c>
       <c r="L126" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128444058131</v>
       </c>
     </row>
     <row r="127">
@@ -6031,7 +6031,7 @@
         <v>125</v>
       </c>
       <c r="L127" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203775551237</v>
       </c>
     </row>
     <row r="128">
@@ -6075,7 +6075,7 @@
         <v>126</v>
       </c>
       <c r="L128" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935601062048</v>
       </c>
     </row>
     <row r="129">
@@ -6119,7 +6119,7 @@
         <v>127</v>
       </c>
       <c r="L129" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493559249912</v>
       </c>
     </row>
     <row r="130">
@@ -6163,7 +6163,7 @@
         <v>128</v>
       </c>
       <c r="L130" t="n">
-        <v>314.1592653589793</v>
+        <v>316.494972694702</v>
       </c>
     </row>
     <row r="131">
@@ -6207,7 +6207,7 @@
         <v>129</v>
       </c>
       <c r="L131" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930155241208</v>
       </c>
     </row>
     <row r="132">
@@ -6251,7 +6251,7 @@
         <v>130</v>
       </c>
       <c r="L132" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203728054277</v>
       </c>
     </row>
     <row r="133">
@@ -6295,7 +6295,7 @@
         <v>131</v>
       </c>
       <c r="L133" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930394303518</v>
       </c>
     </row>
     <row r="134">
@@ -6339,7 +6339,7 @@
         <v>132</v>
       </c>
       <c r="L134" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935606424712</v>
       </c>
     </row>
     <row r="135">
@@ -6383,7 +6383,7 @@
         <v>133</v>
       </c>
       <c r="L135" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935556519403</v>
       </c>
     </row>
     <row r="136">
@@ -6427,7 +6427,7 @@
         <v>134</v>
       </c>
       <c r="L136" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949723969125</v>
       </c>
     </row>
     <row r="137">
@@ -6471,7 +6471,7 @@
         <v>135</v>
       </c>
       <c r="L137" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930131088363</v>
       </c>
     </row>
     <row r="138">
@@ -6515,7 +6515,7 @@
         <v>136</v>
       </c>
       <c r="L138" t="n">
-        <v>314.1592653589793</v>
+        <v>333.612843067546</v>
       </c>
     </row>
     <row r="139">
@@ -6559,7 +6559,7 @@
         <v>137</v>
       </c>
       <c r="L139" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203929243579</v>
       </c>
     </row>
     <row r="140">
@@ -6603,7 +6603,7 @@
         <v>138</v>
       </c>
       <c r="L140" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930435469172</v>
       </c>
     </row>
     <row r="141">
@@ -6647,7 +6647,7 @@
         <v>139</v>
       </c>
       <c r="L141" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935579793537</v>
       </c>
     </row>
     <row r="142">
@@ -6691,7 +6691,7 @@
         <v>140</v>
       </c>
       <c r="L142" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949720419701</v>
       </c>
     </row>
     <row r="143">
@@ -6735,7 +6735,7 @@
         <v>141</v>
       </c>
       <c r="L143" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930149451188</v>
       </c>
     </row>
     <row r="144">
@@ -6779,7 +6779,7 @@
         <v>142</v>
       </c>
       <c r="L144" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128434232093</v>
       </c>
     </row>
     <row r="145">
@@ -6823,7 +6823,7 @@
         <v>143</v>
       </c>
       <c r="L145" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930368598884</v>
       </c>
     </row>
     <row r="146">
@@ -6867,7 +6867,7 @@
         <v>144</v>
       </c>
       <c r="L146" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930352462348</v>
       </c>
     </row>
     <row r="147">
@@ -6911,7 +6911,7 @@
         <v>145</v>
       </c>
       <c r="L147" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935624048642</v>
       </c>
     </row>
     <row r="148">
@@ -6955,7 +6955,7 @@
         <v>146</v>
       </c>
       <c r="L148" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949720782128</v>
       </c>
     </row>
     <row r="149">
@@ -6999,7 +6999,7 @@
         <v>147</v>
       </c>
       <c r="L149" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128411906258</v>
       </c>
     </row>
     <row r="150">
@@ -7043,7 +7043,7 @@
         <v>148</v>
       </c>
       <c r="L150" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199948966973</v>
       </c>
     </row>
     <row r="151">
@@ -7087,7 +7087,7 @@
         <v>149</v>
       </c>
       <c r="L151" t="n">
-        <v>314.1592653589793</v>
+        <v>316.52000357171</v>
       </c>
     </row>
     <row r="152">
@@ -7131,7 +7131,7 @@
         <v>150</v>
       </c>
       <c r="L152" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493554793686</v>
       </c>
     </row>
     <row r="153">
@@ -7175,7 +7175,7 @@
         <v>151</v>
       </c>
       <c r="L153" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935631209669</v>
       </c>
     </row>
     <row r="154">
@@ -7219,7 +7219,7 @@
         <v>152</v>
       </c>
       <c r="L154" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949730207582</v>
       </c>
     </row>
     <row r="155">
@@ -7263,7 +7263,7 @@
         <v>153</v>
       </c>
       <c r="L155" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930139927847</v>
       </c>
     </row>
     <row r="156">
@@ -7307,7 +7307,7 @@
         <v>154</v>
       </c>
       <c r="L156" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199937486802</v>
       </c>
     </row>
     <row r="157">
@@ -7351,7 +7351,7 @@
         <v>155</v>
       </c>
       <c r="L157" t="n">
-        <v>314.1592653589793</v>
+        <v>316.52000357171</v>
       </c>
     </row>
     <row r="158">
@@ -7395,7 +7395,7 @@
         <v>156</v>
       </c>
       <c r="L158" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935538703842</v>
       </c>
     </row>
     <row r="159">
@@ -7439,7 +7439,7 @@
         <v>157</v>
       </c>
       <c r="L159" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935635860169</v>
       </c>
     </row>
     <row r="160">
@@ -7483,7 +7483,7 @@
         <v>158</v>
       </c>
       <c r="L160" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949711683918</v>
       </c>
     </row>
     <row r="161">
@@ -7527,7 +7527,7 @@
         <v>159</v>
       </c>
       <c r="L161" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930134083589</v>
       </c>
     </row>
     <row r="162">
@@ -7571,7 +7571,7 @@
         <v>160</v>
       </c>
       <c r="L162" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199951526662</v>
       </c>
     </row>
     <row r="163">
@@ -7615,7 +7615,7 @@
         <v>161</v>
       </c>
       <c r="L163" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199988886924</v>
       </c>
     </row>
     <row r="164">
@@ -7659,7 +7659,7 @@
         <v>162</v>
       </c>
       <c r="L164" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930346558558</v>
       </c>
     </row>
     <row r="165">
@@ -7703,7 +7703,7 @@
         <v>163</v>
       </c>
       <c r="L165" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935638957113</v>
       </c>
     </row>
     <row r="166">
@@ -7747,7 +7747,7 @@
         <v>164</v>
       </c>
       <c r="L166" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949725176785</v>
       </c>
     </row>
     <row r="167">
@@ -7791,7 +7791,7 @@
         <v>165</v>
       </c>
       <c r="L167" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930162708293</v>
       </c>
     </row>
     <row r="168">
@@ -7835,7 +7835,7 @@
         <v>166</v>
       </c>
       <c r="L168" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128437266337</v>
       </c>
     </row>
     <row r="169">
@@ -7879,7 +7879,7 @@
         <v>167</v>
       </c>
       <c r="L169" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199976839511</v>
       </c>
     </row>
     <row r="170">
@@ -7923,7 +7923,7 @@
         <v>168</v>
       </c>
       <c r="L170" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935527530178</v>
       </c>
     </row>
     <row r="171">
@@ -7967,7 +7967,7 @@
         <v>169</v>
       </c>
       <c r="L171" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949742216135</v>
       </c>
     </row>
     <row r="172">
@@ -8011,7 +8011,7 @@
         <v>170</v>
       </c>
       <c r="L172" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949732469999</v>
       </c>
     </row>
     <row r="173">
@@ -8055,7 +8055,7 @@
         <v>171</v>
       </c>
       <c r="L173" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930093159879</v>
       </c>
     </row>
     <row r="174">
@@ -8099,7 +8099,7 @@
         <v>172</v>
       </c>
       <c r="L174" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128455922499</v>
       </c>
     </row>
     <row r="175">
@@ -8143,7 +8143,7 @@
         <v>173</v>
       </c>
       <c r="L175" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5200030779104</v>
       </c>
     </row>
     <row r="176">
@@ -8187,7 +8187,7 @@
         <v>174</v>
       </c>
       <c r="L176" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930382537314</v>
       </c>
     </row>
     <row r="177">
@@ -8231,7 +8231,7 @@
         <v>175</v>
       </c>
       <c r="L177" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935642771987</v>
       </c>
     </row>
     <row r="178">
@@ -8275,7 +8275,7 @@
         <v>176</v>
       </c>
       <c r="L178" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949678910973</v>
       </c>
     </row>
     <row r="179">
@@ -8319,7 +8319,7 @@
         <v>177</v>
       </c>
       <c r="L179" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930073063024</v>
       </c>
     </row>
     <row r="180">
@@ -8363,7 +8363,7 @@
         <v>178</v>
       </c>
       <c r="L180" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128510561173</v>
       </c>
     </row>
     <row r="181">
@@ -8407,7 +8407,7 @@
         <v>179</v>
       </c>
       <c r="L181" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203762938673</v>
       </c>
     </row>
     <row r="182">
@@ -8451,7 +8451,7 @@
         <v>180</v>
       </c>
       <c r="L182" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930483601277</v>
       </c>
     </row>
     <row r="183">
@@ -8495,7 +8495,7 @@
         <v>181</v>
       </c>
       <c r="L183" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935643124924</v>
       </c>
     </row>
     <row r="184">
@@ -8539,7 +8539,7 @@
         <v>182</v>
       </c>
       <c r="L184" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949758159229</v>
       </c>
     </row>
     <row r="185">
@@ -8583,7 +8583,7 @@
         <v>183</v>
       </c>
       <c r="L185" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930096605775</v>
       </c>
     </row>
     <row r="186">
@@ -8627,7 +8627,7 @@
         <v>184</v>
       </c>
       <c r="L186" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199922130111</v>
       </c>
     </row>
     <row r="187">
@@ -8671,7 +8671,7 @@
         <v>185</v>
       </c>
       <c r="L187" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5200020058144</v>
       </c>
     </row>
     <row r="188">
@@ -8715,7 +8715,7 @@
         <v>186</v>
       </c>
       <c r="L188" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935571797668</v>
       </c>
     </row>
     <row r="189">
@@ -8759,7 +8759,7 @@
         <v>187</v>
       </c>
       <c r="L189" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935637803072</v>
       </c>
     </row>
     <row r="190">
@@ -8803,7 +8803,7 @@
         <v>188</v>
       </c>
       <c r="L190" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949668814854</v>
       </c>
     </row>
     <row r="191">
@@ -8847,7 +8847,7 @@
         <v>189</v>
       </c>
       <c r="L191" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930102842295</v>
       </c>
     </row>
     <row r="192">
@@ -8891,7 +8891,7 @@
         <v>190</v>
       </c>
       <c r="L192" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128432614034</v>
       </c>
     </row>
     <row r="193">
@@ -8935,7 +8935,7 @@
         <v>191</v>
       </c>
       <c r="L193" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930379822863</v>
       </c>
     </row>
     <row r="194">
@@ -8979,7 +8979,7 @@
         <v>192</v>
       </c>
       <c r="L194" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930396575569</v>
       </c>
     </row>
     <row r="195">
@@ -9023,7 +9023,7 @@
         <v>193</v>
       </c>
       <c r="L195" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935645498888</v>
       </c>
     </row>
     <row r="196">
@@ -9067,7 +9067,7 @@
         <v>194</v>
       </c>
       <c r="L196" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949693440503</v>
       </c>
     </row>
     <row r="197">
@@ -9111,7 +9111,7 @@
         <v>195</v>
       </c>
       <c r="L197" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930067068296</v>
       </c>
     </row>
     <row r="198">
@@ -9155,7 +9155,7 @@
         <v>196</v>
       </c>
       <c r="L198" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128419659346</v>
       </c>
     </row>
     <row r="199">
@@ -9199,7 +9199,7 @@
         <v>197</v>
       </c>
       <c r="L199" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5200003965199</v>
       </c>
     </row>
     <row r="200">
@@ -9243,7 +9243,7 @@
         <v>198</v>
       </c>
       <c r="L200" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930389283926</v>
       </c>
     </row>
     <row r="201">
@@ -9287,7 +9287,7 @@
         <v>199</v>
       </c>
       <c r="L201" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935597695209</v>
       </c>
     </row>
     <row r="202">
@@ -9331,7 +9331,7 @@
         <v>200</v>
       </c>
       <c r="L202" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930136072915</v>
       </c>
     </row>
     <row r="203">
@@ -9375,7 +9375,7 @@
         <v>201</v>
       </c>
       <c r="L203" t="n">
-        <v>314.1592653589793</v>
+        <v>333.612836414746</v>
       </c>
     </row>
     <row r="204">
@@ -9419,7 +9419,7 @@
         <v>202</v>
       </c>
       <c r="L204" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128479994617</v>
       </c>
     </row>
     <row r="205">
@@ -9463,7 +9463,7 @@
         <v>203</v>
       </c>
       <c r="L205" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203852380529</v>
       </c>
     </row>
     <row r="206">
@@ -9507,7 +9507,7 @@
         <v>204</v>
       </c>
       <c r="L206" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493038226619</v>
       </c>
     </row>
     <row r="207">
@@ -9551,7 +9551,7 @@
         <v>205</v>
       </c>
       <c r="L207" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935677602443</v>
       </c>
     </row>
     <row r="208">
@@ -9595,7 +9595,7 @@
         <v>206</v>
       </c>
       <c r="L208" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949650285195</v>
       </c>
     </row>
     <row r="209">
@@ -9639,7 +9639,7 @@
         <v>207</v>
       </c>
       <c r="L209" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930070820501</v>
       </c>
     </row>
     <row r="210">
@@ -9683,7 +9683,7 @@
         <v>208</v>
       </c>
       <c r="L210" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199845927224</v>
       </c>
     </row>
     <row r="211">
@@ -9727,7 +9727,7 @@
         <v>209</v>
       </c>
       <c r="L211" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5199921168011</v>
       </c>
     </row>
     <row r="212">
@@ -9771,7 +9771,7 @@
         <v>210</v>
       </c>
       <c r="L212" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930399009428</v>
       </c>
     </row>
     <row r="213">
@@ -9815,7 +9815,7 @@
         <v>211</v>
       </c>
       <c r="L213" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935629652515</v>
       </c>
     </row>
     <row r="214">
@@ -9859,7 +9859,7 @@
         <v>212</v>
       </c>
       <c r="L214" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493015470463</v>
       </c>
     </row>
     <row r="215">
@@ -9903,7 +9903,7 @@
         <v>213</v>
       </c>
       <c r="L215" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930058133309</v>
       </c>
     </row>
     <row r="216">
@@ -9947,7 +9947,7 @@
         <v>214</v>
       </c>
       <c r="L216" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128469647055</v>
       </c>
     </row>
     <row r="217">
@@ -9991,7 +9991,7 @@
         <v>215</v>
       </c>
       <c r="L217" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5200010784708</v>
       </c>
     </row>
     <row r="218">
@@ -10035,7 +10035,7 @@
         <v>216</v>
       </c>
       <c r="L218" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930419411776</v>
       </c>
     </row>
     <row r="219">
@@ -10079,7 +10079,7 @@
         <v>217</v>
       </c>
       <c r="L219" t="n">
-        <v>314.1592653589793</v>
+        <v>316.494964929225</v>
       </c>
     </row>
     <row r="220">
@@ -10123,7 +10123,7 @@
         <v>218</v>
       </c>
       <c r="L220" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949705238832</v>
       </c>
     </row>
     <row r="221">
@@ -10167,7 +10167,7 @@
         <v>219</v>
       </c>
       <c r="L221" t="n">
-        <v>314.1592653589793</v>
+        <v>333.6128453526853</v>
       </c>
     </row>
     <row r="222">
@@ -10211,7 +10211,7 @@
         <v>220</v>
       </c>
       <c r="L222" t="n">
-        <v>314.1592653589793</v>
+        <v>333.612837611058</v>
       </c>
     </row>
     <row r="223">
@@ -10255,7 +10255,7 @@
         <v>221</v>
       </c>
       <c r="L223" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493030620344</v>
       </c>
     </row>
     <row r="224">
@@ -10299,7 +10299,7 @@
         <v>222</v>
       </c>
       <c r="L224" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930420173263</v>
       </c>
     </row>
     <row r="225">
@@ -10343,7 +10343,7 @@
         <v>223</v>
       </c>
       <c r="L225" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935558629183</v>
       </c>
     </row>
     <row r="226">
@@ -10387,7 +10387,7 @@
         <v>224</v>
       </c>
       <c r="L226" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949640409076</v>
       </c>
     </row>
     <row r="227">
@@ -10431,7 +10431,7 @@
         <v>225</v>
       </c>
       <c r="L227" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930048520816</v>
       </c>
     </row>
     <row r="228">
@@ -10475,7 +10475,7 @@
         <v>226</v>
       </c>
       <c r="L228" t="n">
-        <v>314.1592653589793</v>
+        <v>320.8585680840091</v>
       </c>
     </row>
     <row r="229">
@@ -10519,7 +10519,7 @@
         <v>227</v>
       </c>
       <c r="L229" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203811689261</v>
       </c>
     </row>
     <row r="230">
@@ -10563,7 +10563,7 @@
         <v>228</v>
       </c>
       <c r="L230" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930409556525</v>
       </c>
     </row>
     <row r="231">
@@ -10607,7 +10607,7 @@
         <v>229</v>
       </c>
       <c r="L231" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949721616582</v>
       </c>
     </row>
     <row r="232">
@@ -10651,7 +10651,7 @@
         <v>230</v>
       </c>
       <c r="L232" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930134460378</v>
       </c>
     </row>
     <row r="233">
@@ -10695,7 +10695,7 @@
         <v>231</v>
       </c>
       <c r="L233" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930117586991</v>
       </c>
     </row>
     <row r="234">
@@ -10739,7 +10739,7 @@
         <v>232</v>
       </c>
       <c r="L234" t="n">
-        <v>314.1592653589793</v>
+        <v>320.8585671402348</v>
       </c>
     </row>
     <row r="235">
@@ -10783,7 +10783,7 @@
         <v>233</v>
       </c>
       <c r="L235" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5203846937026</v>
       </c>
     </row>
     <row r="236">
@@ -10827,7 +10827,7 @@
         <v>234</v>
       </c>
       <c r="L236" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935568350299</v>
       </c>
     </row>
     <row r="237">
@@ -10871,7 +10871,7 @@
         <v>235</v>
       </c>
       <c r="L237" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935577535929</v>
       </c>
     </row>
     <row r="238">
@@ -10915,7 +10915,7 @@
         <v>236</v>
       </c>
       <c r="L238" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949662303686</v>
       </c>
     </row>
     <row r="239">
@@ -10959,7 +10959,7 @@
         <v>237</v>
       </c>
       <c r="L239" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493011151319</v>
       </c>
     </row>
     <row r="240">
@@ -11003,7 +11003,7 @@
         <v>238</v>
       </c>
       <c r="L240" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5153685157389</v>
       </c>
     </row>
     <row r="241">
@@ -11047,7 +11047,7 @@
         <v>239</v>
       </c>
       <c r="L241" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930404458148</v>
       </c>
     </row>
     <row r="242">
@@ -11091,7 +11091,7 @@
         <v>240</v>
       </c>
       <c r="L242" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935543142448</v>
       </c>
     </row>
     <row r="243">
@@ -11135,7 +11135,7 @@
         <v>241</v>
       </c>
       <c r="L243" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935526149376</v>
       </c>
     </row>
     <row r="244">
@@ -11179,7 +11179,7 @@
         <v>242</v>
       </c>
       <c r="L244" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949747675478</v>
       </c>
     </row>
     <row r="245">
@@ -11223,7 +11223,7 @@
         <v>243</v>
       </c>
       <c r="L245" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930121826131</v>
       </c>
     </row>
     <row r="246">
@@ -11267,7 +11267,7 @@
         <v>244</v>
       </c>
       <c r="L246" t="n">
-        <v>314.1592653589793</v>
+        <v>326.2334607100112</v>
       </c>
     </row>
     <row r="247">
@@ -11311,7 +11311,7 @@
         <v>245</v>
       </c>
       <c r="L247" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5156936442623</v>
       </c>
     </row>
     <row r="248">
@@ -11355,7 +11355,7 @@
         <v>246</v>
       </c>
       <c r="L248" t="n">
-        <v>314.1592653589793</v>
+        <v>316.493045232507</v>
       </c>
     </row>
     <row r="249">
@@ -11399,7 +11399,7 @@
         <v>247</v>
       </c>
       <c r="L249" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949722656391</v>
       </c>
     </row>
     <row r="250">
@@ -11443,7 +11443,7 @@
         <v>248</v>
       </c>
       <c r="L250" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949654888835</v>
       </c>
     </row>
     <row r="251">
@@ -11487,7 +11487,7 @@
         <v>249</v>
       </c>
       <c r="L251" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930056206598</v>
       </c>
     </row>
     <row r="252">
@@ -11531,7 +11531,7 @@
         <v>250</v>
       </c>
       <c r="L252" t="n">
-        <v>314.1592653589793</v>
+        <v>326.233457029243</v>
       </c>
     </row>
     <row r="253">
@@ -11575,7 +11575,7 @@
         <v>251</v>
       </c>
       <c r="L253" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5153737442754</v>
       </c>
     </row>
     <row r="254">
@@ -11619,7 +11619,7 @@
         <v>252</v>
       </c>
       <c r="L254" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930414080699</v>
       </c>
     </row>
     <row r="255">
@@ -11663,7 +11663,7 @@
         <v>253</v>
       </c>
       <c r="L255" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935539511534</v>
       </c>
     </row>
     <row r="256">
@@ -11707,7 +11707,7 @@
         <v>254</v>
       </c>
       <c r="L256" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949651359452</v>
       </c>
     </row>
     <row r="257">
@@ -11751,7 +11751,7 @@
         <v>255</v>
       </c>
       <c r="L257" t="n">
-        <v>314.1592653589793</v>
+        <v>326.2334643536874</v>
       </c>
     </row>
     <row r="258">
@@ -11795,7 +11795,7 @@
         <v>256</v>
       </c>
       <c r="L258" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5266930890054</v>
       </c>
     </row>
     <row r="259">
@@ -11839,7 +11839,7 @@
         <v>257</v>
       </c>
       <c r="L259" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5266857109433</v>
       </c>
     </row>
     <row r="260">
@@ -11883,7 +11883,7 @@
         <v>258</v>
       </c>
       <c r="L260" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930365270935</v>
       </c>
     </row>
     <row r="261">
@@ -11927,7 +11927,7 @@
         <v>259</v>
       </c>
       <c r="L261" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935555479319</v>
       </c>
     </row>
     <row r="262">
@@ -11971,7 +11971,7 @@
         <v>260</v>
       </c>
       <c r="L262" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949675569472</v>
       </c>
     </row>
     <row r="263">
@@ -12015,7 +12015,7 @@
         <v>261</v>
       </c>
       <c r="L263" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930070974885</v>
       </c>
     </row>
     <row r="264">
@@ -12059,7 +12059,7 @@
         <v>262</v>
       </c>
       <c r="L264" t="n">
-        <v>314.1592653589793</v>
+        <v>353.8522755462858</v>
       </c>
     </row>
     <row r="265">
@@ -12103,7 +12103,7 @@
         <v>263</v>
       </c>
       <c r="L265" t="n">
-        <v>314.1592653589793</v>
+        <v>316.515365025322</v>
       </c>
     </row>
     <row r="266">
@@ -12147,7 +12147,7 @@
         <v>264</v>
       </c>
       <c r="L266" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930512409626</v>
       </c>
     </row>
     <row r="267">
@@ -12191,7 +12191,7 @@
         <v>265</v>
       </c>
       <c r="L267" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4935586474806</v>
       </c>
     </row>
     <row r="268">
@@ -12235,7 +12235,7 @@
         <v>266</v>
       </c>
       <c r="L268" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949735091312</v>
       </c>
     </row>
     <row r="269">
@@ -12279,7 +12279,7 @@
         <v>267</v>
       </c>
       <c r="L269" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930338221844</v>
       </c>
     </row>
     <row r="270">
@@ -12323,7 +12323,7 @@
         <v>268</v>
       </c>
       <c r="L270" t="n">
-        <v>314.1592653589793</v>
+        <v>326.2337572852122</v>
       </c>
     </row>
     <row r="271">
@@ -12367,7 +12367,7 @@
         <v>269</v>
       </c>
       <c r="L271" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5157071668045</v>
       </c>
     </row>
     <row r="272">
@@ -12411,7 +12411,7 @@
         <v>270</v>
       </c>
       <c r="L272" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4930995056035</v>
       </c>
     </row>
     <row r="273">
@@ -12455,7 +12455,7 @@
         <v>271</v>
       </c>
       <c r="L273" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949982632948</v>
       </c>
     </row>
     <row r="274">
@@ -12499,7 +12499,7 @@
         <v>272</v>
       </c>
       <c r="L274" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949949448641</v>
       </c>
     </row>
     <row r="275">
@@ -12543,7 +12543,7 @@
         <v>273</v>
       </c>
       <c r="L275" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4931225342144</v>
       </c>
     </row>
     <row r="276">
@@ -12587,7 +12587,7 @@
         <v>274</v>
       </c>
       <c r="L276" t="n">
-        <v>314.1592653589793</v>
+        <v>353.8720428264945</v>
       </c>
     </row>
     <row r="277">
@@ -12631,7 +12631,7 @@
         <v>275</v>
       </c>
       <c r="L277" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5154609790848</v>
       </c>
     </row>
     <row r="278">
@@ -12675,7 +12675,7 @@
         <v>276</v>
       </c>
       <c r="L278" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4932882082629</v>
       </c>
     </row>
     <row r="279">
@@ -12719,7 +12719,7 @@
         <v>277</v>
       </c>
       <c r="L279" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4938104361505</v>
       </c>
     </row>
     <row r="280">
@@ -12763,7 +12763,7 @@
         <v>278</v>
       </c>
       <c r="L280" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4951729044798</v>
       </c>
     </row>
   </sheetData>
